--- a/MAJSushiConfig/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -29,7 +29,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/ConceptMap/FRHealthProfessionalLMCDAFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/ConceptMap/FRHealthProfessionalLMCDAFHIR</t>
   </si>
   <si>
     <t>Version</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -174,7 +174,7 @@
     <t>Person.name</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHumanName</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHumanName|0.1.0</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-name|0.1.0</t>

--- a/MAJSushiConfig/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="81">
   <si>
     <t>Property</t>
   </si>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t>FRLMHealthProfessional.name</t>
+  </si>
+  <si>
+    <t>FRLMHumanName</t>
   </si>
   <si>
     <t>Person.name</t>
@@ -682,12 +685,14 @@
       <c r="A3" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" t="s" s="2">
+        <v>49</v>
+      </c>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -720,7 +725,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -729,7 +734,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -737,79 +742,79 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -851,7 +856,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -866,7 +871,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -879,7 +884,7 @@
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -892,20 +897,20 @@
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -947,7 +952,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -962,7 +967,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -975,7 +980,7 @@
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -983,12 +988,14 @@
       <c r="A5" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" t="s" s="2">
+        <v>49</v>
+      </c>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1001,7 +1008,7 @@
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1014,7 +1021,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1047,7 +1054,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1056,7 +1063,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -1064,53 +1071,53 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" s="2"/>
     </row>
